--- a/Practice/01. Test-Original-Vid-1 (Font + Alignment).xlsx
+++ b/Practice/01. Test-Original-Vid-1 (Font + Alignment).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5688" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -236,11 +236,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -534,16 +534,16 @@
   <sheetData>
     <row r="1" spans="2:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
     </row>
     <row r="3" spans="2:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
     </row>
     <row r="4" spans="2:5" s="5" customFormat="1" ht="27" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="11" t="s">
@@ -60648,21 +60648,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="B2:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+    <row r="2" spans="2:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="D2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
